--- a/marketer_forms/007_website_onboarding_form--marketer_forms.xlsx
+++ b/marketer_forms/007_website_onboarding_form--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'small',_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'small', 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'large',_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'large', 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'x-large',_'label':_'x-large'}</t>
+          <t>x-large</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'x-large', 'label': 'X-Large'}</t>
+          <t>X-Large</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'finance',_'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'finance', 'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'technology',_'label':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'technology', 'label': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'marketing',_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'marketing', 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'e-commerce',_'label':_'e-commerce'}</t>
+          <t>e-commerce</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'e-commerce', 'label': 'E-commerce'}</t>
+          <t>E-commerce</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'s-corporation',_'label':_'s-corporation'}</t>
+          <t>s-corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 's-corporation', 'label': 'S-Corporation'}</t>
+          <t>S-Corporation</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'c-corporation',_'label':_'c-corporation'}</t>
+          <t>c-corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'c-corporation', 'label': 'C-Corporation'}</t>
+          <t>C-Corporation</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'sole-proprietorship',_'label':_'sole-proprietorship'}</t>
+          <t>sole-proprietorship</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'sole-proprietorship', 'label': 'Sole-Proprietorship'}</t>
+          <t>Sole-Proprietorship</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'partnership',_'label':_'partnership'}</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'partnership', 'label': 'Partnership'}</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'united_states',_'label':_'united_states'}</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'united_states', 'label': 'United States'}</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_'canada',_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': 'Canada', 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'north_america',_'label':_'north_america'}</t>
+          <t>north_america</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'north_america', 'label': 'North America'}</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_28,_'name':_'south_america',_'label':_'south_america'}</t>
+          <t>south_america</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 28, 'name': 'south_america', 'label': 'South America'}</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_29,_'name':_'europe',_'label':_'europe'}</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 29, 'name': 'europe', 'label': 'Europe'}</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'asia',_'label':_'asia'}</t>
+          <t>asia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'asia', 'label': 'Asia'}</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'e-shop',_'label':_'e-shop'}</t>
+          <t>e-shop</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'e-shop', 'label': 'E-shop'}</t>
+          <t>E-shop</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'blog',_'label':_'blog'}</t>
+          <t>blog</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'blog', 'label': 'Blog'}</t>
+          <t>Blog</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'finance',_'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'finance', 'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_34,_'name':_'technology',_'label':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 34, 'name': 'technology', 'label': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_35,_'name':_'marketing',_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 35, 'name': 'marketing', 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_36,_'name':_'e-commerce',_'label':_'e-commerce'}</t>
+          <t>e-commerce</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 36, 'name': 'e-commerce', 'label': 'E-commerce'}</t>
+          <t>E-commerce</t>
         </is>
       </c>
     </row>
